--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_17_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_17_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2506</v>
+        <v>7.9247</v>
       </c>
       <c r="E2" t="n">
-        <v>7.6441</v>
+        <v>8.351800000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3935</v>
+        <v>-0.4271</v>
       </c>
       <c r="G2" t="n">
         <v>5.0923</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3</v>
+        <v>0.9741</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.326</v>
+        <v>0.3817</v>
       </c>
       <c r="U2" t="n">
-        <v>0.626</v>
+        <v>0.5924</v>
       </c>
       <c r="V2" t="n">
         <v>0.9304</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6422</v>
+        <v>4.6339</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2207</v>
+        <v>3.6492</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4215</v>
+        <v>0.9846</v>
       </c>
       <c r="G3" t="n">
         <v>2.7516</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5706</v>
+        <v>-0.579</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.963</v>
+        <v>-0.5344</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3923</v>
+        <v>-0.0446</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7377</v>
+        <v>3.0331</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6812</v>
+        <v>2.963</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9435</v>
+        <v>0.0701</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3407</v>
+        <v>-0.8395</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6132</v>
+        <v>2.4764</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9539</v>
+        <v>-3.3158</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0385</v>
+        <v>1.1118</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1344</v>
+        <v>3.2132</v>
       </c>
       <c r="L4" t="n">
-        <v>2.9041</v>
+        <v>-2.1014</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6978</v>
+        <v>-1.9513</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7477</v>
+        <v>-0.7369</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-1.2144</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1365</v>
+        <v>1.035</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0351</v>
+        <v>0.6372</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1013</v>
+        <v>0.3978</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4695</v>
+        <v>2.9297</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2986</v>
+        <v>3.638</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1709</v>
+        <v>-0.7083</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8395</v>
+        <v>1.3407</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4764</v>
+        <v>-0.6132</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.3158</v>
+        <v>1.9539</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1118</v>
+        <v>3.0385</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2132</v>
+        <v>0.1344</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.1014</v>
+        <v>2.9041</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9513</v>
+        <v>-1.6978</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7369</v>
+        <v>-0.7477</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2144</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4714</v>
+        <v>-0.9445</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>-0.0784</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4986</v>
+        <v>-0.8661</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.306</v>
+        <v>2.8622</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7592</v>
+        <v>4.3489</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4531</v>
+        <v>-1.4867</v>
       </c>
       <c r="G6" t="n">
         <v>2.8003</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2016</v>
+        <v>0.7578</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0668</v>
+        <v>0.523</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2684</v>
+        <v>0.2348</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2038</v>
+        <v>0.872</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0827</v>
+        <v>0.5493</v>
       </c>
       <c r="F7" t="n">
-        <v>0.121</v>
+        <v>0.3227</v>
       </c>
       <c r="G7" t="n">
         <v>-0.731</v>
@@ -1000,13 +1000,13 @@
         <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2931</v>
+        <v>0.9614</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2571</v>
+        <v>0.7237</v>
       </c>
       <c r="U7" t="n">
-        <v>0.036</v>
+        <v>0.2377</v>
       </c>
       <c r="V7" t="n">
         <v>-1.214</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2226</v>
+        <v>-0.3234</v>
       </c>
       <c r="E8" t="n">
         <v>-1.242</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0195</v>
+        <v>0.9187</v>
       </c>
       <c r="G8" t="n">
         <v>0.3165</v>
@@ -1078,13 +1078,13 @@
         <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0846</v>
+        <v>0.9838</v>
       </c>
       <c r="T8" t="n">
         <v>0.4876</v>
       </c>
       <c r="U8" t="n">
-        <v>0.597</v>
+        <v>0.4962</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7429</v>
+        <v>-1.0554</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1541</v>
+        <v>-1.2923</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.8969</v>
+        <v>0.2369</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6127</v>
+        <v>-0.7301</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3986</v>
+        <v>-0.1512</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.214</v>
+        <v>-0.5788</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1785</v>
+        <v>0.0168</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6617</v>
+        <v>0.0168</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8402</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7912</v>
+        <v>-0.7469</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7369</v>
+        <v>-0.168</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0543</v>
+        <v>-0.5788</v>
       </c>
       <c r="P9" t="n">
         <v>-0.232</v>
@@ -1156,28 +1156,28 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1018</v>
+        <v>-0.0934</v>
       </c>
       <c r="T9" t="n">
-        <v>1.9935</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8918</v>
+        <v>0.056</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.089</v>
+        <v>-1.6028</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2923</v>
+        <v>1.0925</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2033</v>
+        <v>-2.6953</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7301</v>
+        <v>-1.6127</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1512</v>
+        <v>-1.3986</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5788</v>
+        <v>-0.214</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0168</v>
+        <v>1.1785</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0168</v>
+        <v>-0.6617</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.8402</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7469</v>
+        <v>-2.7912</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.168</v>
+        <v>-0.7369</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5788</v>
+        <v>-2.0543</v>
       </c>
       <c r="P10" t="n">
         <v>-0.232</v>
@@ -1234,22 +1234,22 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.127</v>
+        <v>0.2418</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1494</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0224</v>
+        <v>-0.6901</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4693</v>
+        <v>-3.2163</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7373</v>
+        <v>-2.3835</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.732</v>
+        <v>-0.8328</v>
       </c>
       <c r="G11" t="n">
         <v>-2.773</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6963</v>
+        <v>-0.4433</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2161</v>
+        <v>0.1377</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4802</v>
+        <v>-0.581</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.261</v>
+        <v>-6.5237</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1087</v>
+        <v>-2.5058</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.1523</v>
+        <v>-4.0178</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2485</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5263</v>
+        <v>0.2636</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5351</v>
+        <v>0.1379</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1256</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0748</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-8.501799999999999</v>
+        <v>-7.8373</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.5536</v>
+        <v>-6.8892</v>
       </c>
       <c r="F13" t="n">
         <v>-0.9481000000000001</v>
@@ -1468,10 +1468,10 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5975</v>
+        <v>0.067</v>
       </c>
       <c r="T13" t="n">
-        <v>0.13</v>
+        <v>0.7945</v>
       </c>
       <c r="U13" t="n">
         <v>-0.7275</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.323200000000003</v>
+        <v>1.696700000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>9.906699999999997</v>
+        <v>10.2799</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.5832</v>
+        <v>-8.5831</v>
       </c>
       <c r="G14" t="n">
         <v>-3.8239</v>
@@ -1516,13 +1516,13 @@
         <v>-5.3965</v>
       </c>
       <c r="I14" t="n">
-        <v>1.572799999999998</v>
+        <v>1.572799999999997</v>
       </c>
       <c r="J14" t="n">
         <v>15.9405</v>
       </c>
       <c r="K14" t="n">
-        <v>2.758499999999999</v>
+        <v>2.758500000000001</v>
       </c>
       <c r="L14" t="n">
         <v>13.182</v>
@@ -1546,13 +1546,13 @@
         <v>18.5563</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8509</v>
+        <v>3.2243</v>
       </c>
       <c r="T14" t="n">
-        <v>3.6197</v>
+        <v>3.9931</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7689000000000001</v>
+        <v>-0.7687999999999997</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1829</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6437</v>
+        <v>3.8745</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2782</v>
+        <v>4.4526</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6345</v>
+        <v>-0.578</v>
       </c>
       <c r="G15" t="n">
         <v>1.3298</v>
@@ -1624,13 +1624,13 @@
         <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7805</v>
+        <v>1.0113</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6948</v>
+        <v>0.8691</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0857</v>
+        <v>0.1421</v>
       </c>
       <c r="V15" t="n">
         <v>0.1418</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7252</v>
+        <v>3.1348</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7272</v>
+        <v>1.8452</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9979</v>
+        <v>1.2896</v>
       </c>
       <c r="G16" t="n">
         <v>1.2646</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2353</v>
+        <v>-0.8257</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0113</v>
+        <v>-0.7196</v>
       </c>
       <c r="V16" t="n">
         <v>1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.147</v>
+        <v>1.2825</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1386</v>
+        <v>1.0289</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2856</v>
+        <v>0.2535</v>
       </c>
       <c r="G17" t="n">
-        <v>3.108</v>
+        <v>0.2682</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0707</v>
+        <v>0.9208</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1787</v>
+        <v>-0.6526</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7116</v>
+        <v>2.788</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3193</v>
+        <v>1.7008</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3923</v>
+        <v>1.0872</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3963</v>
+        <v>-2.5198</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.39</v>
+        <v>-0.78</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7863</v>
+        <v>-1.7398</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6237</v>
+        <v>3.0154</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8913</v>
+        <v>-0.2693</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2987</v>
+        <v>-0.0272</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5926</v>
+        <v>-0.242</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>0.8197</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. FORREST</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8633999999999999</v>
+        <v>1.2707</v>
       </c>
       <c r="E18" t="n">
-        <v>2.8177</v>
+        <v>-0.1386</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9543</v>
+        <v>1.4093</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1367</v>
+        <v>3.108</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8571</v>
+        <v>-0.0707</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9937</v>
+        <v>3.1787</v>
       </c>
       <c r="J18" t="n">
-        <v>2.6689</v>
+        <v>2.7116</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1868</v>
+        <v>0.3193</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4821</v>
+        <v>2.3923</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8056</v>
+        <v>0.3963</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3298</v>
+        <v>-0.39</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4759</v>
+        <v>0.7863</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1598</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>1.7655</v>
+        <v>-0.7677</v>
       </c>
       <c r="T18" t="n">
-        <v>1.3961</v>
+        <v>-0.2987</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3695</v>
+        <v>-0.4689</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0018</v>
+        <v>0.2205</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1802</v>
+        <v>3.2982</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.1785</v>
+        <v>-3.0776</v>
       </c>
       <c r="G19" t="n">
         <v>0.9191</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1672</v>
+        <v>-0.9484</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6642</v>
+        <v>-0.5463</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.503</v>
+        <v>-0.4022</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6778999999999999</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>T. FORREST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2889</v>
+        <v>-0.0402</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0853</v>
+        <v>1.9921</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3742</v>
+        <v>-2.0323</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2682</v>
+        <v>-0.1367</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9208</v>
+        <v>0.8571</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6526</v>
+        <v>-0.9937</v>
       </c>
       <c r="J20" t="n">
-        <v>2.788</v>
+        <v>2.6689</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7008</v>
+        <v>1.1868</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0872</v>
+        <v>1.4821</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5198</v>
+        <v>-2.8056</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.78</v>
+        <v>-0.3298</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7398</v>
+        <v>-2.4759</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>3.0154</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8407</v>
+        <v>0.8619</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>0.5704</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8698</v>
+        <v>0.2915</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8197</v>
+        <v>0.3943</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8197</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4147</v>
+        <v>-0.5276</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-1.0298</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1433</v>
+        <v>0.5022</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5003</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6282</v>
+        <v>-0.7411</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3383</v>
+        <v>-0.1336</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9665</v>
+        <v>-0.6075</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6778999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5009</v>
+        <v>-1.1857</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0336</v>
+        <v>-1.7977</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5327</v>
+        <v>0.612</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6755</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8254</v>
+        <v>-0.5102</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.452</v>
+        <v>-0.3727</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. DIALLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5233</v>
+        <v>-2.0332</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8186</v>
+        <v>-1.4873</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7046</v>
+        <v>-0.5458</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.451</v>
+        <v>-1.1324</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2592</v>
+        <v>-0.6338</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.7101</v>
+        <v>-0.4986</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3036</v>
+        <v>0.5725</v>
       </c>
       <c r="K23" t="n">
-        <v>1.9059</v>
+        <v>0.0707</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.5018</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7546</v>
+        <v>-1.7049</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3532</v>
+        <v>-0.7045</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.1078</v>
+        <v>-1.0004</v>
       </c>
       <c r="P23" t="n">
-        <v>-4.1751</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.639</v>
+        <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>1.4945</v>
+        <v>0.7745</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9085</v>
+        <v>0.2596</v>
       </c>
       <c r="U23" t="n">
-        <v>0.586</v>
+        <v>0.5149</v>
       </c>
       <c r="V23" t="n">
-        <v>1.6083</v>
+        <v>-0.2836</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>H. DIALLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.472</v>
+        <v>-2.6622</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1951</v>
+        <v>-1.6443</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.277</v>
+        <v>-1.0179</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1324</v>
+        <v>-0.451</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.6338</v>
+        <v>2.2592</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4986</v>
+        <v>-2.7101</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5725</v>
+        <v>1.3036</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0707</v>
+        <v>1.9059</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5018</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7049</v>
+        <v>-1.7546</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7045</v>
+        <v>0.3532</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0004</v>
+        <v>-2.1078</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3917</v>
+        <v>-4.1751</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3356</v>
+        <v>0.3556</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4481</v>
+        <v>0.0828</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7837</v>
+        <v>0.2728</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2836</v>
+        <v>1.6083</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5047</v>
+        <v>-3.0849</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3699</v>
+        <v>0.4558</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.1348</v>
+        <v>-3.5407</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1698</v>
@@ -2404,13 +2404,13 @@
         <v>0.6959</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.639</v>
+        <v>-0.2192</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5895</v>
+        <v>0.2361</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0495</v>
+        <v>-0.4553</v>
       </c>
       <c r="V25" t="n">
         <v>-1.0722</v>
@@ -2437,19 +2437,19 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.323399999999999</v>
+        <v>0.2492000000000005</v>
       </c>
       <c r="E26" t="n">
-        <v>6.974799999999999</v>
+        <v>6.9751</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.298400000000001</v>
+        <v>-6.7257</v>
       </c>
       <c r="G26" t="n">
         <v>3.824000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>5.396799999999999</v>
+        <v>5.3968</v>
       </c>
       <c r="I26" t="n">
         <v>-1.5725</v>
@@ -2467,7 +2467,7 @@
         <v>-15.9407</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.7586</v>
+        <v>-2.758599999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-13.1821</v>
@@ -2482,13 +2482,13 @@
         <v>15.0771</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.851</v>
+        <v>-1.2783</v>
       </c>
       <c r="T26" t="n">
-        <v>0.7689000000000002</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.619800000000001</v>
+        <v>-2.0469</v>
       </c>
       <c r="V26" t="n">
         <v>1.1829</v>
